--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>20.06707010747188</v>
+        <v>3.260898892464181</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9746760271644</v>
+        <v>2.758384854414216</v>
       </c>
       <c r="E2" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F2" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.21369245657607</v>
+        <v>3.772225024193612</v>
       </c>
       <c r="D3" t="n">
-        <v>21.39652908861456</v>
+        <v>3.476935976899866</v>
       </c>
       <c r="E3" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F3" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.43002126015387</v>
+        <v>2.344878454775004</v>
       </c>
       <c r="D4" t="n">
-        <v>12.31895978588639</v>
+        <v>2.001830965206538</v>
       </c>
       <c r="E4" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F4" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.35427908094435</v>
+        <v>5.582570350653457</v>
       </c>
       <c r="D5" t="n">
-        <v>36.60275187392805</v>
+        <v>5.947947179513308</v>
       </c>
       <c r="E5" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F5" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.5236301516398</v>
+        <v>4.635089899641468</v>
       </c>
       <c r="D6" t="n">
-        <v>16.55479468653824</v>
+        <v>2.690154136562464</v>
       </c>
       <c r="E6" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F6" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.4522467298021</v>
+        <v>6.248490093592841</v>
       </c>
       <c r="D7" t="n">
-        <v>38.96028606529308</v>
+        <v>6.331046485610126</v>
       </c>
       <c r="E7" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F7" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.97544801545492</v>
+        <v>7.308510302511425</v>
       </c>
       <c r="D8" t="n">
-        <v>18.39119870688358</v>
+        <v>2.988569789868582</v>
       </c>
       <c r="E8" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F8" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.16137605418227</v>
+        <v>3.601223608804618</v>
       </c>
       <c r="D9" t="n">
-        <v>21.88376097895557</v>
+        <v>3.556111159080281</v>
       </c>
       <c r="E9" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F9" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.18178917387859</v>
+        <v>5.717040740755271</v>
       </c>
       <c r="D10" t="n">
-        <v>34.65550823256999</v>
+        <v>5.631520087792624</v>
       </c>
       <c r="E10" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F10" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>29.72553997716234</v>
+        <v>4.83040024628888</v>
       </c>
       <c r="D11" t="n">
-        <v>29.85872031766418</v>
+        <v>4.85204205162043</v>
       </c>
       <c r="E11" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F11" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81431040281205</v>
+        <v>4.194825440456959</v>
       </c>
       <c r="D12" t="n">
-        <v>25.49244054426545</v>
+        <v>4.142521588443135</v>
       </c>
       <c r="E12" t="n">
-        <v>8.49744986662918</v>
+        <v>1.380835603327242</v>
       </c>
       <c r="F12" t="n">
-        <v>8.576757515207639</v>
+        <v>1.393723096221241</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
